--- a/AAII_Financials/Yearly/JCSE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/JCSE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
   <si>
     <t>JCSE</t>
   </si>
@@ -952,7 +952,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-3200</v>
+        <v>-3100</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="E20" s="3">
         <v>-400</v>
@@ -1657,7 +1657,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-800</v>
+        <v>-700</v>
       </c>
       <c r="E32" s="3">
         <v>400</v>
@@ -2159,8 +2159,8 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>600</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>3</v>
@@ -2370,7 +2370,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E52" s="3">
         <v>2700</v>
@@ -2532,7 +2532,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="E57" s="3">
         <v>400</v>
@@ -2616,7 +2616,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4700</v>
+        <v>4800</v>
       </c>
       <c r="E59" s="3">
         <v>5300</v>
